--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AAFDA93-A77D-4277-85B2-39ECBFA78F06}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70C1E10A-E556-486A-A49A-C54796DDC3DC}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3180" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -110,6 +110,60 @@
   </si>
   <si>
     <t>Requires BIOS config to determine which card to use</t>
+  </si>
+  <si>
+    <t>Watching</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gmmPfDCRfrQ</t>
+  </si>
+  <si>
+    <t>How Kanban works, practices</t>
+  </si>
+  <si>
+    <t>Visualise everything. To do/In progress/done boards?</t>
+  </si>
+  <si>
+    <t>Found 3 sources</t>
+  </si>
+  <si>
+    <t>https://www.atlassian.com/agile/kanban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Found some best practices, what it intends to solve, and </t>
+  </si>
+  <si>
+    <t>https://allthingsagile.co/post/kanban-practices-and-principles/</t>
+  </si>
+  <si>
+    <t>Briefly read, seems to have a lot of info already covered by previous sources</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=rnMToOThBuk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seems for intended for software development/cyclical/iterative approach, which the team has expressed a distaste for. </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=W94eceurqAQ</t>
+  </si>
+  <si>
+    <t>How to actually get started with Kanban</t>
+  </si>
+  <si>
+    <t>Intended for organisation that already have an existing process and customer base, rather than a new group. Not particularly  useful.</t>
+  </si>
+  <si>
+    <t>Finding AI Digital Forensics tools</t>
+  </si>
+  <si>
+    <t>7 sources found an briefly examined</t>
+  </si>
+  <si>
+    <t>https://aiforensics.org/</t>
+  </si>
+  <si>
+    <t>Is about investigating AI, rather than using AI to investigate. Not useful.</t>
   </si>
 </sst>
 </file>
@@ -171,7 +225,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -180,10 +234,14 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -469,55 +527,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G15"/>
+  <dimension ref="B2:G20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
     <col min="3" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="76.140625" customWidth="1"/>
-    <col min="6" max="6" width="52.140625" customWidth="1"/>
+    <col min="5" max="5" width="53.42578125" customWidth="1"/>
+    <col min="6" max="6" width="74.28515625" customWidth="1"/>
     <col min="7" max="7" width="131" customWidth="1"/>
     <col min="8" max="8" width="33.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -565,12 +623,166 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="7">
+        <v>46248</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="7">
+        <v>46248</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="7">
+        <v>46248</v>
+      </c>
+      <c r="C12" s="1">
+        <v>15</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="7">
+        <v>46248</v>
+      </c>
+      <c r="C13" s="1">
+        <v>20</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F14" s="1"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F15" s="1"/>
+      <c r="B14" s="7">
+        <v>46248</v>
+      </c>
+      <c r="C14" s="1">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B15" s="7">
+        <v>46248</v>
+      </c>
+      <c r="C15" s="1">
+        <v>15</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="C16" s="1">
+        <v>15</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C19" s="1">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="C20" s="1">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70C1E10A-E556-486A-A49A-C54796DDC3DC}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8925ED19-939A-44BF-AD61-80039C5BD7A7}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26940" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -160,10 +160,10 @@
     <t>7 sources found an briefly examined</t>
   </si>
   <si>
+    <t>Is about investigating AI, rather than using AI to investigate. Not useful.</t>
+  </si>
+  <si>
     <t>https://aiforensics.org/</t>
-  </si>
-  <si>
-    <t>Is about investigating AI, rather than using AI to investigate. Not useful.</t>
   </si>
 </sst>
 </file>
@@ -173,7 +173,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/mm/yy;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,6 +193,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -225,7 +232,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -242,6 +249,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -729,6 +743,9 @@
       </c>
     </row>
     <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B16" s="3">
+        <v>46248</v>
+      </c>
       <c r="C16" s="1">
         <v>15</v>
       </c>
@@ -745,44 +762,51 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="8">
         <v>46251</v>
       </c>
+      <c r="C18" s="9">
+        <v>10</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C19" s="1">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>10</v>
+      <c r="B19" s="8"/>
+      <c r="C19" s="9">
+        <v>5</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="C20" s="1">
-        <v>5</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" t="s">
-        <v>33</v>
-      </c>
+      <c r="B20" s="8"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8925ED19-939A-44BF-AD61-80039C5BD7A7}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8939C78A-2C13-4FFF-9B35-7460BFAC23C8}"/>
   <bookViews>
-    <workbookView xWindow="-26940" yWindow="0" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
   <si>
     <t>Date</t>
   </si>
@@ -164,6 +164,24 @@
   </si>
   <si>
     <t>https://aiforensics.org/</t>
+  </si>
+  <si>
+    <t>6 sources found</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=P6BfVaxqbOw</t>
+  </si>
+  <si>
+    <t>Indepth knowledge on cyclical processes and stages.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JrREE2SebPU</t>
+  </si>
+  <si>
+    <t>Finding out what Design Science is</t>
+  </si>
+  <si>
+    <t>Originally in German so translation wasn't perfect. Gave insights about design processes. Turns out it’s a Research methodology, not a PM one.</t>
   </si>
 </sst>
 </file>
@@ -232,30 +250,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -541,15 +561,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G20"/>
+  <dimension ref="B2:G23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.140625" style="3" customWidth="1"/>
-    <col min="3" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="53.42578125" customWidth="1"/>
-    <col min="6" max="6" width="74.28515625" customWidth="1"/>
-    <col min="7" max="7" width="131" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="13.140625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="23.85546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="53.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="74.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="131" style="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
@@ -558,9 +580,9 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -570,7 +592,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -593,37 +615,37 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="3">
+    <row r="7" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
         <v>46234</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>10</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="3">
+      <c r="B8" s="2">
         <v>46234</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>5</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -633,17 +655,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="7">
+      <c r="B10" s="2">
         <v>46248</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="7">
+      <c r="B11" s="2">
         <v>46248</v>
       </c>
       <c r="C11" s="1">
@@ -663,7 +681,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="7">
+      <c r="B12" s="2">
         <v>46248</v>
       </c>
       <c r="C12" s="1">
@@ -683,7 +701,7 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="7">
+      <c r="B13" s="2">
         <v>46248</v>
       </c>
       <c r="C13" s="1">
@@ -703,7 +721,7 @@
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="7">
+      <c r="B14" s="2">
         <v>46248</v>
       </c>
       <c r="C14" s="1">
@@ -723,7 +741,7 @@
       </c>
     </row>
     <row r="15" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="7">
+      <c r="B15" s="2">
         <v>46248</v>
       </c>
       <c r="C15" s="1">
@@ -738,12 +756,12 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="B16" s="3">
+      <c r="B16" s="2">
         <v>46248</v>
       </c>
       <c r="C16" s="1">
@@ -758,7 +776,7 @@
       <c r="F16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="1" t="s">
         <v>28</v>
       </c>
     </row>
@@ -766,47 +784,109 @@
       <c r="B18" s="8">
         <v>46251</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="3">
         <v>10</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="8"/>
-      <c r="C19" s="9">
+      <c r="B19" s="8">
+        <v>46251</v>
+      </c>
+      <c r="C19" s="3">
         <v>5</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="3" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C21" s="1">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C22" s="1">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B23" s="2">
+        <v>46255</v>
+      </c>
+      <c r="C23" s="1">
+        <v>15</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>38</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="144" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8939C78A-2C13-4FFF-9B35-7460BFAC23C8}"/>
+  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE134818-40E9-4B09-9CCE-B92EA48F00BF}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -182,6 +182,18 @@
   </si>
   <si>
     <t>Originally in German so translation wasn't perfect. Gave insights about design processes. Turns out it’s a Research methodology, not a PM one.</t>
+  </si>
+  <si>
+    <t>What AI is good/bad at in Digital Forensics, for use in selecting test cases .</t>
+  </si>
+  <si>
+    <t>2 Sources found.</t>
+  </si>
+  <si>
+    <t>Found out what specifically AI has issues with when it comes to DF. Good for formulating test cases on.</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2666281725001830</t>
   </si>
 </sst>
 </file>
@@ -561,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G23"/>
+  <dimension ref="B2:G26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -580,7 +592,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -592,7 +604,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -888,6 +900,46 @@
         <v>38</v>
       </c>
     </row>
+    <row r="25" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B25" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C25" s="1">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>46259</v>
+      </c>
+      <c r="C26" s="1">
+        <v>60</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="161" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE134818-40E9-4B09-9CCE-B92EA48F00BF}"/>
+  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FB24E4-B74C-480A-9DFB-F1CC3B4A6D8C}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
   <si>
     <t>Date</t>
   </si>
@@ -195,6 +195,95 @@
   <si>
     <t>https://www.sciencedirect.com/science/article/pii/S2666281725001830</t>
   </si>
+  <si>
+    <t>How to implement Design Science</t>
+  </si>
+  <si>
+    <t>5 sources found</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Peffers, K., Tuunanen, T., Rothenberger, M., &amp; Chatterjee, S. (2007). A design science research methodology for information systems research. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Journal of Management Information Systems</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(3), 45–77.</t>
+    </r>
+  </si>
+  <si>
+    <t>Widely cited, has become default process model for Design Science research. Gives researches a structure instead of ad hoc justification. Cool because you can start at 4 different points, instead of treating it as a linear process.</t>
+  </si>
+  <si>
+    <t>Margolis, A., Schmidt, S. L., Böckel, A., &amp; Blomsma, F. (2026). Applying design science in creativity and innovation management research: A decision guide for deepening research practice. Creativity and Innovation Management. https://doi.org/10.1111/caim.70049</t>
+  </si>
+  <si>
+    <t>Not directly applicable, but does support DSR as a live evolving methodology.</t>
+  </si>
+  <si>
+    <t>Listening to audio</t>
+  </si>
+  <si>
+    <t>van der Merwe, A., Gerber, A., &amp; Smuts, H. (2020). Guidelines for conducting design science research in information systems. In B. Tait, J. Kroeze, &amp; S. Gruner (Eds.), ICT Education (SACLA 2019, Communications in Computer and Information Science, Vol. 1136, pp. 163–178). Springer. https://doi.org/10.1007/978-3-030-35629-3_11</t>
+  </si>
+  <si>
+    <t>Good secondary source. Cites Peffers et al.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LTMucsu35dk</t>
+  </si>
+  <si>
+    <t>https://www.holmsecurity.com/blog/what-is-nmap</t>
+  </si>
+  <si>
+    <t>What is Nmap, how does it work, how to use it.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=4t4kBkMsDbQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=JHNgjZzY0DE</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fMdei5VbJMc</t>
+  </si>
 </sst>
 </file>
 
@@ -203,7 +292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d/mm/yy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -230,6 +319,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -262,7 +359,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -288,6 +385,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -573,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -592,7 +690,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -940,6 +1038,171 @@
         <v>44</v>
       </c>
     </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B29" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C29" s="1">
+        <v>75</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C30" s="1">
+        <v>20</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="2">
+        <v>46262</v>
+      </c>
+      <c r="C31" s="1">
+        <v>25</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C33" s="1">
+        <v>25</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C34" s="1">
+        <v>10</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B35" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C35" s="1">
+        <v>25</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C36" s="1">
+        <v>30</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="2">
+        <v>46264</v>
+      </c>
+      <c r="C37" s="1">
+        <v>25</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="247" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3FB24E4-B74C-480A-9DFB-F1CC3B4A6D8C}"/>
+  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FC6B8A-5DB6-44D8-9AC9-B25EBFE46BF8}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -283,6 +283,24 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=fMdei5VbJMc</t>
+  </si>
+  <si>
+    <t>Good guide on using nmap and checking ports.</t>
+  </si>
+  <si>
+    <t>Shows how to configure tools for effective use.</t>
+  </si>
+  <si>
+    <t>Shows differences between stealth and aggressive modes, how to detect operating systems.</t>
+  </si>
+  <si>
+    <t>Marketing content, so not as useful. Does have good plain english explanations</t>
+  </si>
+  <si>
+    <t>Seems aimed for network attacks. Not as useful.</t>
+  </si>
+  <si>
+    <t>RC - as directed by Bryce</t>
   </si>
 </sst>
 </file>
@@ -385,7 +403,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -671,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G37"/>
+  <dimension ref="B2:G39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1094,7 +1112,7 @@
       <c r="F30" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" t="s">
         <v>49</v>
       </c>
     </row>
@@ -1114,7 +1132,7 @@
       <c r="F31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1131,8 +1149,11 @@
       <c r="E33" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="F33" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="G33" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
@@ -1148,11 +1169,14 @@
       <c r="E34" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="F34" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="G34" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B35" s="2">
         <v>46264</v>
       </c>
@@ -1164,6 +1188,9 @@
       </c>
       <c r="E35" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>57</v>
@@ -1182,6 +1209,9 @@
       <c r="E36" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="F36" s="1" t="s">
+        <v>61</v>
+      </c>
       <c r="G36" s="1" t="s">
         <v>58</v>
       </c>
@@ -1199,8 +1229,16 @@
       <c r="E37" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>59</v>
+      <c r="F37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E39" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="261" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60FC6B8A-5DB6-44D8-9AC9-B25EBFE46BF8}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B1645A-6B3D-473E-A336-2EE98DC7CBFA}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
   <si>
     <t>Date</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>RC - as directed by Bryce</t>
+  </si>
+  <si>
+    <t>WinSCP</t>
   </si>
 </sst>
 </file>
@@ -689,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G39"/>
+  <dimension ref="B2:G41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -1241,6 +1244,11 @@
         <v>65</v>
       </c>
     </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E41" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8B1645A-6B3D-473E-A336-2EE98DC7CBFA}"/>
+  <xr:revisionPtr revIDLastSave="361" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4472CD17-0E06-4813-821D-CE9F54C942B4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -300,10 +300,76 @@
     <t>Seems aimed for network attacks. Not as useful.</t>
   </si>
   <si>
-    <t>RC - as directed by Bryce</t>
-  </si>
-  <si>
-    <t>WinSCP</t>
+    <t>RC - As directed by Dr Bryce</t>
+  </si>
+  <si>
+    <t>How to use WinSCP to move files to remote machine</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0O-Z0BRiJF8</t>
+  </si>
+  <si>
+    <t>Useful. Managed to get the local and remote windows working, can upload.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NyMRVbGtM5w</t>
+  </si>
+  <si>
+    <t>Seems like a good AI, but it needs to be paid for and seems intended for larger teams and requires more resources. Not useful for this project.</t>
+  </si>
+  <si>
+    <t>Not useful, this is pure marketing.</t>
+  </si>
+  <si>
+    <t>https://www.energent.ai/use-cases/en/compare/ai-tools-for-forensic-analysis</t>
+  </si>
+  <si>
+    <t>Useful, pointed me in the direction of qwen3.8 and deepseek-r1.</t>
+  </si>
+  <si>
+    <t>Claude Sonnet 5</t>
+  </si>
+  <si>
+    <t>5 sources found and examined</t>
+  </si>
+  <si>
+    <t>What are good AI models for analysing Digital Forensics files?</t>
+  </si>
+  <si>
+    <t>Useful, suggests Mistral-7B. Flags a Local vs Cloud based speed tradeoff, which is something to talk about as we can only use local AI due to the nature of DF.</t>
+  </si>
+  <si>
+    <t>Not as useful, doesn't mention any models explicitly. Does list various types of dataset that may be useful however</t>
+  </si>
+  <si>
+    <t>https://www.researchgate.net/publication/379867130_AI-Enhanced_Digital_Forensics_Automated_Techniques_for_Efficient_Investigation_and_Evidence_Collection</t>
+  </si>
+  <si>
+    <t>Ethical considerations of AI in DF</t>
+  </si>
+  <si>
+    <t>https://belkasoft.com/using-ai-and-ml-for-dfir</t>
+  </si>
+  <si>
+    <t>Useful. We have to track which tool and version was used, what the prompt was, and decide what counts as evidence (don't let the machine do it).</t>
+  </si>
+  <si>
+    <t>Condusive to group and advisor communication, useful cultural touchstone.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5nS_2zA-kDw</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=m9SMGLminrU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=d6m69sN26pE</t>
+  </si>
+  <si>
+    <t>How to use Wireshark, pro tips.</t>
+  </si>
+  <si>
+    <t>add these hours later VVV</t>
   </si>
 </sst>
 </file>
@@ -380,7 +446,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -406,7 +472,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -692,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G41"/>
+  <dimension ref="B2:G53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -711,7 +776,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -723,7 +788,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1235,18 +1300,241 @@
       <c r="F37" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G37" s="9" t="s">
+      <c r="G37" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="39" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C39" s="1">
+        <v>20</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C40" s="1">
+        <v>25</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C41" s="1">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="2">
+        <v>46267</v>
+      </c>
+      <c r="C42" s="1">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C44" s="1">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B45" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C45" s="1">
+        <v>60</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C46" s="1">
+        <v>60</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B47" s="2">
+        <v>46268</v>
+      </c>
+      <c r="C47" s="1">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="C48" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="2">
+        <v>46270</v>
+      </c>
+      <c r="C49" s="1">
+        <v>60</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="E41" s="1" t="s">
-        <v>66</v>
+      <c r="F49" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="2">
+        <v>46271</v>
+      </c>
+      <c r="C51" s="1">
+        <v>45</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B52" s="2">
+        <v>46271</v>
+      </c>
+      <c r="C52" s="1">
+        <v>25</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B53" s="2">
+        <v>46271</v>
+      </c>
+      <c r="C53" s="1">
+        <v>120</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="361" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4472CD17-0E06-4813-821D-CE9F54C942B4}"/>
+  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E97EE7-A907-4992-8539-0A9173C146A0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E97EE7-A907-4992-8539-0A9173C146A0}"/>
+  <xr:revisionPtr revIDLastSave="388" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{505DDE84-89F6-4E7F-AE14-CCC48A35C529}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
   <si>
     <t>Date</t>
   </si>
@@ -370,6 +370,33 @@
   </si>
   <si>
     <t>add these hours later VVV</t>
+  </si>
+  <si>
+    <t>How to integrate Wireshark with AI.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=gMzRl1ovoko</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=ugrfLrL_j0Q</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=PIOM-pD-8KY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Mzk5eF5lirQ</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=UW_ss7Ry1co</t>
+  </si>
+  <si>
+    <t>Useful, shows how you can get an AI to read a pcap file.</t>
+  </si>
+  <si>
+    <t>Not as useful, as it features uploading the pcap file to ChatGPT, while we have to keep everything offline.</t>
+  </si>
+  <si>
+    <t>Covers a lot of the basics. Taking a wireshark capture and uploading it to chatGPT, which we cannot do.</t>
   </si>
 </sst>
 </file>
@@ -446,7 +473,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -472,6 +499,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -757,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G53"/>
+  <dimension ref="B2:G59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -776,7 +804,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -788,7 +816,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1537,6 +1565,85 @@
         <v>86</v>
       </c>
     </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C55" s="1">
+        <v>15</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B56" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C56" s="1">
+        <v>15</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B57" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C57" s="1">
+        <v>25</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B58" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C58" s="1">
+        <v>10</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" s="9" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B59" s="2">
+        <v>46273</v>
+      </c>
+      <c r="C59" s="1">
+        <v>20</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="388" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{505DDE84-89F6-4E7F-AE14-CCC48A35C529}"/>
+  <xr:revisionPtr revIDLastSave="422" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A64DCB78-CDC2-4AA2-8E79-9AF9C3314765}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Research template" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="109">
   <si>
     <t>Date</t>
   </si>
@@ -369,9 +369,6 @@
     <t>How to use Wireshark, pro tips.</t>
   </si>
   <si>
-    <t>add these hours later VVV</t>
-  </si>
-  <si>
     <t>How to integrate Wireshark with AI.</t>
   </si>
   <si>
@@ -397,6 +394,42 @@
   </si>
   <si>
     <t>Covers a lot of the basics. Taking a wireshark capture and uploading it to chatGPT, which we cannot do.</t>
+  </si>
+  <si>
+    <t>Builds on the first video, with AI being able to detect an infected machine. Needs much prompting to find the specific user account though.</t>
+  </si>
+  <si>
+    <t>Covers much of what the other videos on this topic did.</t>
+  </si>
+  <si>
+    <t>How well does AI handle DF report writing?</t>
+  </si>
+  <si>
+    <t>Helpful. Output quality depends on the model used, and some models take a long time.</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2666281723002020#article</t>
+  </si>
+  <si>
+    <t>https://www.sciencedirect.com/science/article/pii/S2666281724001860</t>
+  </si>
+  <si>
+    <t>Helpful, points out the high points of what Ais should be focused on.</t>
+  </si>
+  <si>
+    <t>How to integrate Nmap with AI.</t>
+  </si>
+  <si>
+    <t>Not especially useful, as it doesn't mention any evaluation/accuracy methods, is built for a ubuntu machine, and links to ChatGPT. May be able to be adapted however</t>
+  </si>
+  <si>
+    <t>https://wazuh.com/blog/nmap-and-chatgpt-security-auditing/</t>
+  </si>
+  <si>
+    <t>https://www.academia.edu/121732072/Nmap_and_AI_Integrating_Artificial_Intelligence_into_Network_Scanning</t>
+  </si>
+  <si>
+    <t>Not very useful, doesn't show a working system, data, or methodology. Mostly seems to be hypotheticals.</t>
   </si>
 </sst>
 </file>
@@ -473,7 +506,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -499,7 +532,6 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -785,7 +817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G59"/>
+  <dimension ref="B2:G64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -804,7 +836,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -816,7 +848,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1492,11 +1524,6 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" spans="2:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="C48" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
     <row r="49" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B49" s="2">
         <v>46270</v>
@@ -1572,14 +1599,17 @@
       <c r="C55" s="1">
         <v>15</v>
       </c>
+      <c r="D55" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E55" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G55" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="56" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1589,14 +1619,17 @@
       <c r="C56" s="1">
         <v>15</v>
       </c>
+      <c r="D56" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="2:7" ht="30" x14ac:dyDescent="0.25">
@@ -1606,28 +1639,37 @@
       <c r="C57" s="1">
         <v>25</v>
       </c>
+      <c r="D57" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.25">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" ht="30" x14ac:dyDescent="0.25">
       <c r="B58" s="2">
         <v>46273</v>
       </c>
       <c r="C58" s="1">
         <v>10</v>
       </c>
+      <c r="D58" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E58" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="9" t="s">
-        <v>93</v>
+      <c r="F58" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G58" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.25">
@@ -1637,11 +1679,97 @@
       <c r="C59" s="1">
         <v>20</v>
       </c>
+      <c r="D59" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="E59" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="F59" s="1" t="s">
+        <v>98</v>
+      </c>
       <c r="G59" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B61" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C61" s="1">
+        <v>20</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B62" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C62" s="1">
+        <v>20</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="B63" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C63" s="1">
+        <v>30</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B64" s="2">
+        <v>46274</v>
+      </c>
+      <c r="C64" s="1">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/Research Logs/Dave/Research Log - Dave.xlsx
+++ b/Research Logs/Dave/Research Log - Dave.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://w2shared-my.sharepoint.com/personal/dave_sushames01_student_wandw_ac_nz/Documents/Documents/Capstone/Research Logs/Dave/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="422" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A64DCB78-CDC2-4AA2-8E79-9AF9C3314765}"/>
+  <xr:revisionPtr revIDLastSave="447" documentId="13_ncr:1_{AF0BDED7-A538-4982-BD37-86F9ACE43960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B606872-97C9-4731-B4C5-BF16F7F083FE}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="165" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="116">
   <si>
     <t>Date</t>
   </si>
@@ -430,6 +430,27 @@
   </si>
   <si>
     <t>Not very useful, doesn't show a working system, data, or methodology. Mostly seems to be hypotheticals.</t>
+  </si>
+  <si>
+    <t>What are magic numbers? (Bryce mentioned Foremost uses these)</t>
+  </si>
+  <si>
+    <t>Useful, explains how they work and why you'd use them.</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Magic_number_(programming)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tXTl1ki6prI</t>
+  </si>
+  <si>
+    <t>Somewhat useful, shows how magic numbers can be used to target specific filetypes.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=pjWXkGhgEmI</t>
+  </si>
+  <si>
+    <t>Useful, demonstrates use of magic numbers for file signatures.</t>
   </si>
 </sst>
 </file>
@@ -817,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G64"/>
+  <dimension ref="B2:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -836,7 +857,7 @@
       </c>
       <c r="D2" s="4">
         <f>ROUNDDOWN(SUM(C7:C500)/60,0)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -848,7 +869,7 @@
       </c>
       <c r="D3" s="4">
         <f>ROUND(MOD(SUM(C7:C500),60),0)</f>
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
@@ -1772,6 +1793,66 @@
         <v>107</v>
       </c>
     </row>
+    <row r="66" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B66" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C66" s="1">
+        <v>20</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="B67" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C67" s="1">
+        <v>10</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B68" s="2">
+        <v>46275</v>
+      </c>
+      <c r="C68" s="1">
+        <v>20</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
